--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:I443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -440,7 +440,8 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,10 +477,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Email Affaires Médicales</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Plateau Coronaro/Interventionnel</t>
         </is>
@@ -513,7 +519,8 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -555,7 +562,12 @@
           <t>p.henon@ch-stquentin.fr</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>c.hugues@ch-stquentin.fr</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -597,7 +609,12 @@
           <t>p.henon@ch-stquentin.fr</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>c.hugues@ch-stquentin.fr</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -631,7 +648,12 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>eric.heyrman@ch-soissons.fr</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -665,7 +687,8 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -707,7 +730,12 @@
           <t>secret.cardio1est@ch-laon.fr</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>benedicte.point@ch-laon.fr</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -741,7 +769,8 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -783,7 +812,12 @@
           <t>adela.fircea@ch-chateau-thierry.fr</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>affaires.medicales@ch-chateau-thierry.fr</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -825,7 +859,12 @@
           <t>vincent.tixier@ch-vichy.fr</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>amandine.bernon@ch-vichy.fr</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -867,7 +906,12 @@
           <t>vincent.tixier@ch-vichy.fr</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>amandine.bernon@ch-vichy.fr</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -909,7 +953,12 @@
           <t>s.chanseaume@ch-montlucon.fr</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>m.demain@ch-montlucon.fr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -951,7 +1000,12 @@
           <t>m.bouchantpioche@ch-moulins-yzeure.fr</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>affaires-medicales@ch-moulins-yzeure.fr</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -993,7 +1047,8 @@
           <t>touria.mghazli@chicas-gap.fr</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1035,7 +1090,8 @@
           <t>jacques.quilici@chicas-gap.fr</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1077,7 +1133,8 @@
           <t>esaggiorato@ch-briancon.fr</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1119,7 +1176,8 @@
           <t>laurent.jacq@ch-antibes.fr</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1153,7 +1211,8 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1187,7 +1246,8 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1229,7 +1289,8 @@
           <t>b.petit@ch-grasse.fr</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1263,7 +1324,8 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1305,7 +1367,8 @@
           <t>nor.el.houda.zelazli@ch-ardeche-meridionale.fr</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1347,7 +1410,12 @@
           <t>thierry.gouttard@ch-ardeche-nord.fr</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>dam.ag@chu-st-etienne.fr</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1376,7 +1444,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Médecine A  /  Cardiologie</t>
+          <t>Médecine A / Cardiologie</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1389,7 +1457,12 @@
           <t>p.charre@ch-privas.fr</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>a.guiraud@ch-privas.fr</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1431,7 +1504,12 @@
           <t>virginie.heroguelle@ch-nord-ardennes.fr</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>aurelie.barbe@ch-nord-ardennes.fr</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1473,7 +1551,12 @@
           <t>joseph.abdo@chi-val-ariege.fr</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>francois.ooghe@chi-val-ariege.fr</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1507,7 +1590,12 @@
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>mathilde.royer@hcs-sante.fr</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1541,7 +1629,8 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1583,7 +1672,12 @@
           <t>youcef.afifi@ch-carcassonne.fr</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>affairesmedicales-cooperations@ch-carcassonne.fr</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1621,7 +1715,8 @@
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1655,7 +1750,8 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1689,7 +1785,8 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1731,7 +1828,8 @@
           <t>t.hassani@ch-rodez.fr</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1765,7 +1863,8 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1799,7 +1898,8 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1833,7 +1933,8 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1867,7 +1968,8 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1901,7 +2003,8 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1935,7 +2038,8 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -1969,7 +2073,8 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2003,7 +2108,8 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2045,7 +2151,8 @@
           <t>jtaieb@ch-aix.fr</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2079,7 +2186,8 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2117,7 +2225,12 @@
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>jennifer.mauriat@ch-salon.fr</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2159,7 +2272,12 @@
           <t>serge.yvorra@ch-martigues.fr</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>janette.belaadi@ch-martigues.fr</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2201,7 +2319,12 @@
           <t>eroux@ch-aubagne.fr</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>margaux.maurel@ch-aubagne.fr</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2243,7 +2366,8 @@
           <t>francois.saint-pierre@ch-arles.fr</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2285,7 +2409,8 @@
           <t>francois.saint-pierre@ch-arles.fr</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2319,7 +2444,8 @@
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2353,7 +2479,8 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2395,7 +2522,8 @@
           <t>beygui-f@chu-caen.fr</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2437,7 +2565,12 @@
           <t>t.werner@ch-lisieux.fr</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>v.dubesset@ch-lisieux.fr</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2479,7 +2612,12 @@
           <t>damrong.ea@ch-falaise.fr</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>lebosse-m@chu-caen.fr</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2521,7 +2659,8 @@
           <t>Aferroudj@ch-cotefleurie.fr</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2563,7 +2702,8 @@
           <t>jpmabire@ch-cotefleurie.fr</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2597,7 +2737,8 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2639,7 +2780,12 @@
           <t>cardiologie@ch-aurillac.fr</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>j.mutin@ch-aurillac.fr</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -2681,7 +2827,8 @@
           <t>m.font@ch-aurillac.fr</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2723,7 +2870,12 @@
           <t>veronique.lucke@ch-angouleme.fr</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>stephanie.jonas@ch-angouleme.fr</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2765,7 +2917,12 @@
           <t>a.alsaleh@ch-cognac.fr</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>j.heraud@ch-cognac.fr</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2807,7 +2964,8 @@
           <t>ludovic.meunier@ght-atlantique17.fr</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2849,7 +3007,12 @@
           <t>caroline.lasgi@gh-saintesangely.fr</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>suzy.ferchaud@gh-saintesangely.fr</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -2891,7 +3054,12 @@
           <t>hatem.berrahmoun@gh-saintesangely.fr</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>suzy.ferchaud@gh-saintesangely.fr</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -2933,7 +3101,12 @@
           <t>noor.bengoufa@gh-saintesangely.fr</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>suzy.ferchaud@gh-saintesangely.fr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -2975,7 +3148,8 @@
           <t>sandra.benigno@ch-rochefort.fr</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3017,7 +3191,8 @@
           <t>abderrahim.harouri@gh-saintesangely.fr</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3059,7 +3234,12 @@
           <t>secretariat.medecinec@ch-royan.fr</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>affaires.medicales@ch-royan.fr</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3101,7 +3281,8 @@
           <t>valerian.didot@ch-bourges.fr</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3135,7 +3316,8 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3177,7 +3359,12 @@
           <t>eric.fleurant@ch-brive.fr</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>sarah.ferret@ch-brive.fr</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3219,7 +3406,12 @@
           <t>guillon@ch-tulle.fr</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>affaires-medicales.tulle@ch-correze.fr</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3261,7 +3453,8 @@
           <t>a.berenfeld@chussel.fr</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3295,7 +3488,12 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>relations.humaines@ch-bastia.fr</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3329,7 +3527,12 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>relations.humaines@ch-bastia.fr</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3363,7 +3566,12 @@
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>relations.humaines@ch-bastia.fr</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3397,7 +3605,12 @@
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>relations.humaines@ch-bastia.fr</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3439,7 +3652,12 @@
           <t>audrey.sagnard@chu-dijon.fr</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>anne-lucie.boulanger@chu-dijon.fr</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3481,7 +3699,12 @@
           <t>helene.greigert@chu-dijon.fr</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>anne-lucie.boulanger@chu-dijon.fr</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3519,7 +3742,12 @@
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>anne-lucie.boulanger@chu-dijon.fr</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3561,7 +3789,12 @@
           <t>aurelie.gudjoncik@ch-beaune.fr</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>marie.fraslin@ch-beaune.fr</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3603,7 +3836,8 @@
           <t>idriss.kioueh@ch-semur.fr</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3645,7 +3879,8 @@
           <t>mohamed.jolak@ch-hco.fr</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3674,12 +3909,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cardiologie / Cardiologie Interventionnelle hôpital de jour /  Hospitalisation de semaine de cardiologie</t>
+          <t>Cardiologie / Cardiologie Interventionnelle hôpital de jour / Hospitalisation de semaine de cardiologie</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>clemence.fourrier@armorsante.bzh</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -3721,7 +3961,8 @@
           <t>annehelene.ginguene@ch-dinan.fr</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3755,7 +3996,8 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3789,7 +4031,8 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3831,7 +4074,12 @@
           <t>guillaume.gosselin@armorsante.bzh</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>clemence.fourrier@armorsante.bzh</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3873,7 +4121,12 @@
           <t>l.mansour@ch-gueret.fr</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>secdrh@ch-gueret.fr</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3915,7 +4168,12 @@
           <t>philippe.jarnier@ch-perigueux.fr</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>florence.fons-atger@ch-perigueux.fr</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3957,7 +4215,12 @@
           <t>philippe.jarnier@ch-perigueux.fr</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>florence.fons-atger@ch-perigueux.fr</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -3999,7 +4262,12 @@
           <t>quanthu.nguyen@ch-perigueux.fr</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>florence.fons-atger@ch-perigueux.fr</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4041,7 +4309,12 @@
           <t>martine.dumain@ch-bergerac.fr</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>lorelei.mirot@ch-bergerac.fr</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4075,7 +4348,12 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>lionel.chevallier@ch-perigueux.fr</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4117,7 +4395,12 @@
           <t>nicolas.meneveau@univ-fcomte.fr</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>kdurupt@chu-besancon.fr</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4159,7 +4442,12 @@
           <t>mrabot@ch-valence.fr</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>fverheyden@ch-valence.fr</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4193,7 +4481,12 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.dam@ghpp.fr</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4227,7 +4520,12 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>p.clavaison@ch-hdn.fr</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4269,7 +4567,8 @@
           <t>c.kugler@dieulefit-sante.org</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4303,7 +4602,12 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>louisa.atmani@ch-eureseine.fr</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4337,7 +4641,12 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>louisa.atmani@ch-eureseine.fr</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4379,7 +4688,12 @@
           <t>eliza.cumminy@ch-bernay.fr</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>marguerite.clement@ch-eureseine.fr</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4421,7 +4735,12 @@
           <t>falbert@ch-chartres.fr</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>ofalanga@ch-chartres.fr</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4463,7 +4782,12 @@
           <t>dbottigliero@ch-dreux.fr</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>averdin@ch-dreux.fr</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4501,7 +4825,8 @@
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4543,7 +4868,8 @@
           <t>jacques.mansourati@chu-brest.fr</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4577,7 +4903,12 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>y.senechal@ch-cornouaille.fr</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4619,7 +4950,8 @@
           <t>eric.legoff@chu-brest.fr</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4653,7 +4985,8 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4695,7 +5028,8 @@
           <t>secretariat.direction@ch-douarnenez.fr</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4737,7 +5071,8 @@
           <t>secretariat.direction@ch-douarnenez.fr</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4779,7 +5114,8 @@
           <t>secretariat.direction@ch-douarnenez.fr</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4817,7 +5153,8 @@
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4859,7 +5196,8 @@
           <t>Mehdi.BOUADJAMA@chu-nimes.fr</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4897,7 +5235,8 @@
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4939,7 +5278,12 @@
           <t>dr.alarcon@ch-ales.fr</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>audrey.perrier@ch-ales.fr</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -4981,7 +5325,8 @@
           <t>oabrieu@ch-bagnolssurceze.fr</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5023,7 +5368,8 @@
           <t>elbaz.m@chu-toulouse.fr</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5065,7 +5411,8 @@
           <t>marcheix.b@chu-toulouse.fr</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5107,7 +5454,8 @@
           <t>karsenty.cl@chu-toulouse.fr</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5149,7 +5497,12 @@
           <t>jeanphilippe.bonnet@ch-saintgaudens.fr</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>johan.berkane@ch-saintgaudens.fr</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5191,7 +5544,12 @@
           <t>m.lescure@ch-auch.fr</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>v.bompart@ch-auch.fr</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5233,7 +5591,8 @@
           <t>jean-michel.haissaguerre@chu-bordeaux.fr</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5267,7 +5626,8 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr">
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5309,7 +5669,8 @@
           <t>raymond.roudaut@chu-bordeaux.fr</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5351,7 +5712,8 @@
           <t>jean-benoit.thambo@chu-bordeaux.fr</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5393,7 +5755,8 @@
           <t>pierre.coste@chu-bordeaux.fr</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -5427,7 +5790,8 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr">
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5469,7 +5833,12 @@
           <t>cardiologie@ch-sudgironde.fr</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>manar.elouafi@ch-cadillac.fr</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5511,7 +5880,8 @@
           <t>jean-michel.haissaguerre@chu-bordeaux.fr</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5553,7 +5923,12 @@
           <t>romain.darier@ch-arcachon.fr</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Vincent.Tortes-Saint-Jammes@ch-arcachon.fr</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5595,7 +5970,12 @@
           <t>nassib.azoury@ch-beziers.fr</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>carole.gleyzes@ch-beziers.fr</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5637,7 +6017,8 @@
           <t>jl-pasquie@chu-montpellier.fr</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5671,7 +6052,12 @@
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>DAM-Secretariat@chu-rennes.fr</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5713,7 +6099,8 @@
           <t>f.revault@ch-stmalo.fr</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5755,7 +6142,8 @@
           <t>f.revault@ch-stmalo.fr</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5797,7 +6185,8 @@
           <t>catherine.vidal@ch-vitre.fr</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5839,7 +6228,8 @@
           <t>alexandru.mischie@ch-chateauroux.fr</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5873,7 +6263,8 @@
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5907,7 +6298,8 @@
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5941,7 +6333,8 @@
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr">
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -5975,7 +6368,8 @@
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr">
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6009,7 +6403,8 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr">
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6043,7 +6438,8 @@
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6077,7 +6473,8 @@
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr">
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6115,7 +6512,12 @@
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>geraldine.ducrocq@hopitaux-jura.fr</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6157,7 +6559,12 @@
           <t>cardio-neuro.cadre@ch-dole.fr</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>olard.alexandra@ch-dole.fr</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6199,7 +6606,12 @@
           <t>medecine.stclaude@hopitaux-jura.fr</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>geraldine.ducrocq@hopitaux-jura.fr</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6233,7 +6645,8 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6267,7 +6680,12 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>simon.beaudrap@ch-dax.fr</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6301,7 +6719,12 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>simon.beaudrap@ch-dax.fr</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6343,7 +6766,12 @@
           <t>alain.ranjatson@ch-mdm.fr</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>candice.berland@ch-mdm.fr</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6385,7 +6813,12 @@
           <t>sec.cardio@ch-blois.fr</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>gallanl@ch-blois.fr</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6419,7 +6852,8 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6461,7 +6895,8 @@
           <t>Antoine.DaCosta@chu-st-etienne.fr</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6503,7 +6938,8 @@
           <t>j.noel.albertini@chu-st-etienne.fr</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6545,7 +6981,12 @@
           <t>secretariat.cardio@ch-roanne.fr</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.cme@ch-roanne.fr</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6579,7 +7020,8 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr">
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6621,7 +7063,12 @@
           <t>mikael.boulot@ch-lepuy.fr</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>sophie.benito@ch-lepuy.fr</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6655,7 +7102,12 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.dam@ch-saintnazaire.fr</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6697,7 +7149,8 @@
           <t>jean-noël.trochu@chu-nantes.fr</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6735,7 +7188,12 @@
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>celine.reuze@ch-cnp.fr</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6769,7 +7227,8 @@
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6803,7 +7262,8 @@
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6845,7 +7305,12 @@
           <t>marc.goralski@chu-orleans.fr</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>olivier.ferrendier@chu-orleans.fr</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6879,7 +7344,12 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>sgrzesiak@ch-montargis.fr</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6921,7 +7391,8 @@
           <t>Mihaela.bucelea@ch-cahors.fr</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6955,7 +7426,12 @@
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.drh@psv47.fr</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -6997,7 +7473,12 @@
           <t>cracanau@ch-agen-nerac.fr</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>martini@ch-agen-nerac.fr</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7031,7 +7512,12 @@
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>martini@ch-agen-nerac.fr</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7065,7 +7551,12 @@
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>michelle.anxolabehere@chicmt.fr</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7099,7 +7590,8 @@
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7141,7 +7633,12 @@
           <t>FaPrunier@chu-angers.fr</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>DAM@chu-angers.fr</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7175,7 +7672,8 @@
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7209,7 +7707,8 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7251,7 +7750,12 @@
           <t>affaires-medicales@ch-saumur.fr</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>laurent.renaut@ch-saumur.fr</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7270,7 +7774,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Centre hospitalier d'Avranches-Granville (Granville)</t>
+          <t>Hôpitaux du Sud-Manche (Granville)</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7293,7 +7797,8 @@
           <t>takieddine.abada@ch-avranches-granville.fr</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7335,7 +7840,12 @@
           <t>p.loiselet@ch-cotentin.fr</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>yann.tanguy@ch-cotentin.fr</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7377,7 +7887,12 @@
           <t>g.malcor@ch-cotentin.fr</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>yann.tanguy@ch-cotentin.fr</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -7419,7 +7934,12 @@
           <t>laurent.michel@ch-stlo.fr</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>laure.salles@ch-stlo.fr</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7461,7 +7981,8 @@
           <t>dmetz@chu-reims.fr</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7503,7 +8024,8 @@
           <t>vgruggieri@chu-reims.fr</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7545,7 +8067,8 @@
           <t>cmarcus@chu-reims.fr</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7587,7 +8110,12 @@
           <t>nbajolle@ch-chalonsenchampagne.fr</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>wchabbaz@ch-chalonsenchampagne.fr</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7629,7 +8157,12 @@
           <t>m.andriambololona@ch-vitrylefrancois.fr</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>celine.ruhland@ch-saintdizier.fr</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7671,7 +8204,12 @@
           <t>olivier.claudon@ch-chaumont.fr</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>xavier.huard@ch-shm.fr</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7705,7 +8243,12 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>celine.ruhland@ch-saintdizier.fr</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7739,7 +8282,12 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>celine.ruhland@ch-saintdizier.fr</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7773,7 +8321,8 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7815,7 +8364,12 @@
           <t>tahar.lazizi@chlaval.fr</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>affaires.medicales@chlaval.fr</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7857,7 +8411,8 @@
           <t>amoumen@ch-mayenne.fr</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7891,7 +8446,8 @@
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr">
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7933,7 +8489,8 @@
           <t>G.BOSSER@chru-nancy.fr</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -7975,7 +8532,8 @@
           <t>n.sadoul@chru-nancy.fr</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8009,7 +8567,8 @@
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8051,7 +8610,8 @@
           <t>jp.maureira@chru-nancy.fr</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8093,7 +8653,8 @@
           <t>n.sadoul@chru-nancy.fr</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8127,7 +8688,8 @@
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr">
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8165,7 +8727,8 @@
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr">
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8199,7 +8762,12 @@
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>celine.ruhland@ch-saintdizier.fr</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8233,7 +8801,12 @@
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>celine.ruhland@ch-saintdizier.fr</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8267,7 +8840,8 @@
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8309,7 +8883,8 @@
           <t>f.porhel@ghbs.bzh</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8343,7 +8918,12 @@
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>armelle.germain@ch-centre-bretagne.fr</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8385,7 +8965,12 @@
           <t>louis-francois.garnier@ch-ploermel.fr</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>maryse.caoudal@ch-bretagne-atlantique.fr</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8427,7 +9012,8 @@
           <t>k.khalife@chr-metz-thionville.fr</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8469,7 +9055,8 @@
           <t>b.schjoth@chr-metz-thionville.fr</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8511,7 +9098,8 @@
           <t>k.khalife@chr-metz-thionville.fr</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8553,7 +9141,8 @@
           <t>mohamed.nessibi@ch-sarreguemines.fr</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8595,7 +9184,8 @@
           <t>awad.alammar@unisante.fr</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8629,7 +9219,8 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr">
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8663,7 +9254,12 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.direction@ch-sarrebourg.fr</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8697,7 +9293,12 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>chan.drh.sec@ght58.fr</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8731,7 +9332,12 @@
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>chan.drh.sec@ght58.fr</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8773,7 +9379,8 @@
           <t>teche.m@ght58.fr</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8807,7 +9414,8 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr">
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8849,7 +9457,12 @@
           <t>rosario.pilato@ch-douai.fr</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>emeline.bertrand@ch-douai.fr</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8891,7 +9504,12 @@
           <t>edecoulx@ch-tourcoing.fr</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>cvasseur@ch-tourcoing.fr</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8925,7 +9543,12 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>amedicales@ch-denain.fr</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -8967,7 +9590,12 @@
           <t>alessandro.cosenza@ghsc.fr</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Clement.ACQUART@ghsc.fr</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9001,7 +9629,8 @@
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr">
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9035,7 +9664,8 @@
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr">
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9069,7 +9699,8 @@
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr">
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9111,7 +9742,8 @@
           <t>p.kone@ch-cambrai.fr</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9153,7 +9785,8 @@
           <t>p.kone@ch-cambrai.fr</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9195,7 +9828,8 @@
           <t>agraou.benaissa@ch-maubeuge.fr</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9229,7 +9863,8 @@
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr">
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9263,7 +9898,8 @@
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr">
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9297,7 +9933,8 @@
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr">
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9331,7 +9968,8 @@
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr">
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9365,7 +10003,8 @@
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr">
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9407,7 +10046,12 @@
           <t>aamiar@chsa.fr</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>fbried@chsa.fr</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9449,7 +10093,8 @@
           <t>f.coviaux@ch-armentieres.fr</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9483,7 +10128,8 @@
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr">
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9517,7 +10163,8 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr">
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9559,7 +10206,12 @@
           <t>j.clerc@ch-compiegnenoyon.fr</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>c.balluais@ch-compiegnenoyon.fr</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9593,7 +10245,12 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>s.salem@ch-beauvais.fr</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9627,7 +10284,8 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr">
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9669,7 +10327,12 @@
           <t>Salim.Belguidoum@ghpso.fr</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Abdoul.BA@ghpso.fr</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9711,7 +10374,12 @@
           <t>direction.flers@ght-cdn.fr</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>chloe.moru@ght-cdn.fr</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9745,7 +10413,12 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>chloe.moru@ght-cdn.fr</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9779,7 +10452,8 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr">
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9813,7 +10487,8 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr">
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9847,7 +10522,8 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr">
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9889,7 +10565,12 @@
           <t>direction@ch-boulogne.fr</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>el.noviant-laffanour@ch-boulogne.fr</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9931,7 +10612,8 @@
           <t>cmycinski@ch-bethune.fr</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -9965,7 +10647,8 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr">
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10007,7 +10690,12 @@
           <t>Francesco.FAVATA@gh-artoisternois.fr</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.direction@gh-artoisternois.fr</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10049,7 +10737,12 @@
           <t>Philippe.PAUQUET@gh-artoisternois.fr</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.direction@gh-artoisternois.fr</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10091,7 +10784,8 @@
           <t>reschalier@chu-clermontferrand.fr</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10133,7 +10827,8 @@
           <t>lcamilleri@chu-clermontferrand.fr</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10175,7 +10870,8 @@
           <t>p.haumont@ch-riom.fr</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10209,7 +10905,8 @@
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr">
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10247,7 +10944,12 @@
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>jdaeschler@ch-cotebasque.fr</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10281,7 +10983,8 @@
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr">
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10319,7 +11022,8 @@
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr">
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10357,7 +11061,8 @@
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr">
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10395,7 +11100,8 @@
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr">
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10429,7 +11135,8 @@
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr">
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10471,7 +11178,12 @@
           <t>sec.cardiologie@ch-haguenau.fr</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>Valentine.SCHALLER@ch-haguenau.fr</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10513,7 +11225,12 @@
           <t>Mounzer.MANSOUR@ghso.fr</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>agnes.schreiner@ghso.fr</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10555,7 +11272,12 @@
           <t>rtheolade@ch-wissembourg.fr</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>dam@ch-haguenau.fr</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10597,7 +11319,12 @@
           <t>rtheolade@ch-wissembourg.fr</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>dam@ch-haguenau.fr</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10631,7 +11358,12 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10665,7 +11397,12 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10703,7 +11440,12 @@
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10737,7 +11479,12 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10771,7 +11518,8 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr">
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10805,7 +11553,8 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr">
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10839,7 +11588,8 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr">
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10873,7 +11623,8 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr">
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10915,7 +11666,12 @@
           <t>secretariat.cardio@hno.fr</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>cpicherel@hno.fr</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -10949,7 +11705,8 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr">
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -10983,7 +11740,8 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr">
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11017,7 +11775,8 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr">
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11051,7 +11810,8 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr">
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -11085,7 +11845,8 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr">
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11119,7 +11880,8 @@
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr">
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11153,7 +11915,8 @@
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr">
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11187,7 +11950,8 @@
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr">
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11221,7 +11985,8 @@
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr">
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11255,7 +12020,8 @@
       </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr">
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11289,7 +12055,8 @@
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr">
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11323,7 +12090,8 @@
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr">
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11365,7 +12133,8 @@
           <t>cardiologie@hiadcssa.org</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11407,7 +12176,8 @@
           <t>pierre.lantelme@chu-lyon.fr</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11449,7 +12219,8 @@
           <t>l.cart@gh70.fr</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11483,7 +12254,8 @@
       </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr">
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11525,7 +12297,8 @@
           <t>ghyanni@hoteldieu-creusot.fr</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11567,7 +12340,8 @@
           <t>P.BUTTARD@ch-autun.fr</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11609,7 +12383,12 @@
           <t>patrick.buttard@ch-chalon71.fr</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>sylvain.rollot@ch-chalon71.fr</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11651,7 +12430,8 @@
           <t>vincent.descotes-genon@ch-metropole-savoie.fr</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11693,7 +12473,8 @@
           <t>lea.carbone@ch-metropole-savoie.fr</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11735,7 +12516,12 @@
           <t>edesjoyaux@ch-annecygenevois.fr</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>amechoud@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11777,7 +12563,12 @@
           <t>edesjoyaux@ch-annecygenevois.fr</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>amechoud@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11815,7 +12606,12 @@
         </is>
       </c>
       <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr">
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>nmenuet@ch-alpes-leman.fr</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11857,7 +12653,8 @@
           <t>rbenderbous@ch-annecygenevois.fr</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11899,7 +12696,12 @@
           <t>Meds_Sec@ch-sallanches-chamonix.fr</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>e.lemiere@ch-sallanches-chamonix.fr</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11941,7 +12743,12 @@
           <t>secretariat-cardiologie@ch-hopitauxduleman.fr</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>affaires-medicales@ch-hopitauxduleman.fr</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -11983,7 +12790,12 @@
           <t>h-vivet@hopitauxduleman.fr</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>affaires-medicales@ch-hopitauxduleman.fr</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12025,7 +12837,8 @@
           <t>mchacornac@ch-annecygenevois.fr</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12063,7 +12876,12 @@
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr">
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12101,7 +12919,12 @@
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr">
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12139,7 +12962,12 @@
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr">
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12177,7 +13005,12 @@
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr">
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12215,7 +13048,12 @@
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr">
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12253,7 +13091,12 @@
         </is>
       </c>
       <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr">
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12291,7 +13134,12 @@
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr">
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12329,7 +13177,12 @@
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr">
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12367,7 +13220,12 @@
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr">
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12405,7 +13263,12 @@
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr">
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>marie-cecile.mocellin@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -12443,7 +13306,12 @@
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr">
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>marie-cecile.mocellin@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12481,7 +13349,12 @@
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr">
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>marie-cecile.mocellin@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12519,7 +13392,12 @@
         </is>
       </c>
       <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr">
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>marie-cecile.mocellin@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12557,7 +13435,12 @@
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr">
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12595,7 +13478,12 @@
         </is>
       </c>
       <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr">
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12633,7 +13521,12 @@
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr">
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12671,7 +13564,12 @@
         </is>
       </c>
       <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr">
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12709,7 +13607,12 @@
         </is>
       </c>
       <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr">
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12747,7 +13650,12 @@
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr">
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12785,7 +13693,12 @@
         </is>
       </c>
       <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr">
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12823,7 +13736,12 @@
         </is>
       </c>
       <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr">
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12861,7 +13779,12 @@
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr">
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12899,7 +13822,12 @@
         </is>
       </c>
       <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr">
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12933,7 +13861,12 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr">
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -12971,7 +13904,12 @@
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr">
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13009,7 +13947,12 @@
         </is>
       </c>
       <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr">
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13047,7 +13990,8 @@
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr">
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13085,7 +14029,12 @@
         </is>
       </c>
       <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr">
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13119,7 +14068,12 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr">
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13157,7 +14111,12 @@
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr">
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>marie.Ayoub@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13195,7 +14154,12 @@
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr">
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>marie.Ayoub@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13233,7 +14197,12 @@
         </is>
       </c>
       <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr">
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>marie.Ayoub@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13271,7 +14240,12 @@
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr">
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13309,7 +14283,12 @@
         </is>
       </c>
       <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr">
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13343,7 +14322,8 @@
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr">
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13381,7 +14361,8 @@
         </is>
       </c>
       <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr">
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13415,7 +14396,8 @@
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr">
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13449,7 +14431,8 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr">
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13491,7 +14474,8 @@
           <t>fabian.tournevache@chi-elbeuf-louviers.fr</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13533,7 +14517,12 @@
           <t>emmanuel.lecluse@ch-havre.fr</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>melanie.couturier@ch-havre.fr</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13575,7 +14564,12 @@
           <t>emmanuel.lecluse@ch-havre.fr</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>melanie.couturier@ch-havre.fr</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13617,7 +14611,12 @@
           <t>chuche@ch-dieppe.fr</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>rdubuisson@ch-dieppe.fr</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13659,7 +14658,8 @@
           <t>philippe.calot@ch-fecamp.fr</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13701,7 +14701,8 @@
           <t>mgerber@ghef.fr</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13739,7 +14740,8 @@
         </is>
       </c>
       <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr">
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13781,7 +14783,8 @@
           <t>cyrus.moini@ghsif.fr</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13819,7 +14822,8 @@
         </is>
       </c>
       <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr">
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13857,7 +14861,8 @@
         </is>
       </c>
       <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr">
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13899,7 +14904,8 @@
           <t>ehaddad@ch-provins.fr</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13933,7 +14939,8 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr">
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -13975,7 +14982,8 @@
           <t>adama.sangare@ch-montereau.fr</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14017,7 +15025,12 @@
           <t>david.berville@ght-yvelinesnord.fr</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>agathe.benoist@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14059,7 +15072,8 @@
           <t>ggibaultgenty@ght78sud.fr</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14101,7 +15115,12 @@
           <t>david.berville@ght-yvelinesnord.fr</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>agathe.benoist@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14143,7 +15162,8 @@
           <t>cchavelas@ght78sud.fr</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14177,7 +15197,8 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr">
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14219,7 +15240,8 @@
           <t>david.berville@ght-yvelinesnord.fr</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14253,7 +15275,12 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr">
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>karine.morin@ch-niort.fr</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14287,7 +15314,8 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr">
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14321,7 +15349,8 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr">
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14355,7 +15384,8 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr">
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14393,7 +15423,8 @@
         </is>
       </c>
       <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr">
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14427,7 +15458,8 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr">
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14469,7 +15501,8 @@
           <t>hautbout.karine@ch-abbeville.fr</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14511,7 +15544,8 @@
           <t>hautbout.karine@ch-abbeville.fr</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14553,7 +15587,8 @@
           <t>cardiovasculaire@ch-corbie.fr</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14587,7 +15622,8 @@
       </c>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr">
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14621,7 +15657,8 @@
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr">
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14655,7 +15692,12 @@
       </c>
       <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr">
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>jeremy.luceno@ch-albi.fr</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14697,7 +15739,12 @@
           <t>n.elhajjaji@ch-montauban.fr</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14739,7 +15786,12 @@
           <t>n.elhajjaji@ch-montauban.fr</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14781,7 +15833,12 @@
           <t>jean-michel.tartiere@ch-toulon.fr</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14823,7 +15880,12 @@
           <t>farid.challal@ch-toulon.fr</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14865,7 +15927,8 @@
           <t>zakarian-h@chi-fsr.fr</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14907,7 +15970,8 @@
           <t>cardiologie@hia-sainte-anne.ssa.msante.fr</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14941,7 +16005,8 @@
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr">
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -14983,7 +16048,8 @@
           <t>daniele.raufast@chu-lyon.fr</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15017,7 +16083,12 @@
       </c>
       <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr">
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>baratier.aurelie@ch-avignon.fr</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15059,7 +16130,12 @@
           <t>p.giraud@ch-cavaillon.fr</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>anne.desroche@ch-cavaillon.fr</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15093,7 +16169,12 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr">
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.dam@chd-vendee.fr</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15131,7 +16212,8 @@
         </is>
       </c>
       <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr">
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15165,7 +16247,8 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr">
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15199,7 +16282,12 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr">
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>corentin.ringot@ght85.fr</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15241,7 +16329,12 @@
           <t>pierre.corbi@chu-poitiers.fr</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>heloise.baux@chu-poitiers.fr</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15283,7 +16376,12 @@
           <t>luc-philippe.christiaens@chu-poitiers.fr</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>heloise.baux@chu-poitiers.fr</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15325,7 +16423,8 @@
           <t>cardiologie@ghnv.fr</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15367,7 +16466,8 @@
           <t>jean-claude.lorenzo@ch-montmorillon.fr</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15405,7 +16505,8 @@
         </is>
       </c>
       <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr">
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15439,7 +16540,12 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr">
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>sec.direction@ch-ed.fr</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15473,7 +16579,12 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
-      <c r="H390" t="inlineStr">
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>sec.direction@ch-ed.fr</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15507,7 +16618,12 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr">
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>helene.marion@ch-remiremont.fr</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15549,7 +16665,12 @@
           <t>jl.meregnani@ch-ouestvosgien.fr</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>e.andrique@ch-ouestvosgien.fr</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15583,7 +16704,8 @@
       </c>
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr">
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15625,7 +16747,8 @@
           <t>dpacaud@ch-sens.fr</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15667,7 +16790,8 @@
           <t>morvan@ch-joigny.fr</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15709,7 +16833,8 @@
           <t>morvan@ch-joigny.fr</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15747,7 +16872,8 @@
         </is>
       </c>
       <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr">
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15789,7 +16915,8 @@
           <t>yoann.lefrancois@hnfc.fr</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15831,7 +16958,12 @@
           <t>brahim.meftout@chsf.fr</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15873,7 +17005,12 @@
           <t>francois.koukoui@ch-sud-francilien.fr</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15911,7 +17048,8 @@
         </is>
       </c>
       <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr">
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15949,7 +17087,8 @@
         </is>
       </c>
       <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr">
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -15987,7 +17126,8 @@
         </is>
       </c>
       <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr">
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16025,7 +17165,8 @@
         </is>
       </c>
       <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr">
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16063,7 +17204,12 @@
         </is>
       </c>
       <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr">
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16097,7 +17243,8 @@
       </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr">
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16131,7 +17278,8 @@
       </c>
       <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr">
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16173,7 +17321,8 @@
           <t>mohand.goudjil@ch-nanterre.fr</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16215,7 +17364,8 @@
           <t>mohand.goudjil@ch-nanterre.fr</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16257,7 +17407,12 @@
           <t>fatima.boukhsibi@ch-rueil.fr</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-rueil.fr</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16299,7 +17454,12 @@
           <t>fatima.boukhsibi@ch-rueil.fr</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-rueil.fr</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16341,7 +17501,12 @@
           <t>cbotella@ch-rivesdeseine.fr</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>direction@ch-rivesdeseine.fr</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16383,7 +17548,12 @@
           <t>francois.walylo@ch-aulnay.fr</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>maxime.lemee@ght-gpne.fr</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16421,7 +17591,8 @@
         </is>
       </c>
       <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr">
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16463,7 +17634,8 @@
           <t>albert.boccara@ght-gpne.fr</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16505,7 +17677,12 @@
           <t>olivier.nallet@ght-gpne.fr</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>maxime.lemee@ght-gpne.fr</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16543,7 +17720,8 @@
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr">
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16581,7 +17759,8 @@
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr">
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16619,7 +17798,12 @@
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr">
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16657,7 +17841,12 @@
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr">
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -16695,7 +17884,12 @@
         </is>
       </c>
       <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr">
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16733,7 +17927,12 @@
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr">
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16767,7 +17966,8 @@
       </c>
       <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr">
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16805,7 +18005,12 @@
         </is>
       </c>
       <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr">
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16843,7 +18048,12 @@
         </is>
       </c>
       <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr">
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16885,7 +18095,12 @@
           <t>emmanuel.salengro@chiv.fr</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>elena.ketterer@chiv.fr</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16927,7 +18142,8 @@
           <t>pole-medical@hia-begin.ssa.mssante.fr</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -16969,7 +18185,8 @@
           <t>veronique.decalf@ght-novo.fr</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17011,7 +18228,8 @@
           <t>nabil.poulos@ch-gonesse.fr</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr">
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17045,7 +18263,12 @@
       </c>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr">
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>sec.drh@ch-simoneveil.fr</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -17087,7 +18310,12 @@
           <t>francois.duclos@ch-argenteuil.fr</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>bianca.dasilvabarreto@ch-argenteuil.fr</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17129,7 +18357,8 @@
           <t>i.moraru@hopital-parc-taverny.fr</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17171,7 +18400,12 @@
           <t>annie.lannuzel@chu-guadeloupe.fr</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17205,7 +18439,12 @@
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
-      <c r="H434" t="inlineStr">
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17247,7 +18486,8 @@
           <t>jocelyn.inamo@chu-martinique.fr</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr">
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17289,7 +18529,8 @@
           <t>jocelyn.inamo@chu-martinique.fr</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17331,7 +18572,8 @@
           <t>yves-kenol.franck@ch-cayenne.fr</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17373,7 +18615,12 @@
           <t>g.yabeta@ch-ouestguyane.fr</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>s.lavenaire@ch-ouestguyane.fr</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17407,7 +18654,8 @@
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr">
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17449,7 +18697,8 @@
           <t>cardiologie@chd-fguyon.fr</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17491,7 +18740,8 @@
           <t>jf-delambre@chd-fguyon.fr</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17533,7 +18783,12 @@
           <t>secretariat.cardiologie@chor.re</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>Ol.MANICON@pso.re</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17575,7 +18830,8 @@
           <t>christophe.legoanvic@cht.pf</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -17586,669 +18842,871 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G375" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G377" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G379" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G433" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G438" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D443" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G443" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G375" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G377" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G379" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G433" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G438" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D443" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G443" r:id="rId868"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
